--- a/data/trending_integrated_20260914_11.xlsx
+++ b/data/trending_integrated_20260914_11.xlsx
@@ -563,79 +563,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6770</v>
+        <v>9670</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+22.87%</t>
+          <t>+22.41%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.01</v>
+        <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="H2" t="n">
-        <v>1.67</v>
+        <v>17.67</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5510</v>
+        <v>7900</v>
       </c>
       <c r="K2" t="n">
-        <v>5910</v>
+        <v>7790</v>
       </c>
       <c r="L2" t="n">
-        <v>7160</v>
+        <v>9710</v>
       </c>
       <c r="M2" t="n">
-        <v>5890</v>
+        <v>7700</v>
       </c>
       <c r="N2" t="n">
-        <v>1.68</v>
+        <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>44999554200</v>
+        <v>185344869450</v>
       </c>
       <c r="P2" t="n">
-        <v>10360</v>
+        <v>22450</v>
       </c>
       <c r="Q2" t="n">
-        <v>2965</v>
+        <v>1760</v>
       </c>
       <c r="R2" t="n">
-        <v>-27000</v>
+        <v>1000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 보안 및 딥페이크 관련주로 언급되나, 차익 실현 매물 및 단기 급등 가능성에 대한 경계 심리 존재.</t>
+          <t>차세대 광반도체 및 광통신 관련주로, SK하이닉스 CPO 광원 이슈와 함께 3분봉 기반 매물대 돌파 및 전고점 돌파 기대감이 높음.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 보안', '딥페이크', '단기 급등']</t>
+          <t>['광반도체', '광통신', 'CPO']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,82 +643,82 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9370</v>
+        <v>6710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+18.61%</t>
+          <t>+21.78%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.28</v>
+        <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>17.67</v>
+        <v>1.67</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7900</v>
+        <v>5510</v>
       </c>
       <c r="K3" t="n">
-        <v>7790</v>
+        <v>5910</v>
       </c>
       <c r="L3" t="n">
-        <v>9650</v>
+        <v>7160</v>
       </c>
       <c r="M3" t="n">
-        <v>7700</v>
+        <v>5890</v>
       </c>
       <c r="N3" t="n">
-        <v>17.95</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>171930570985</v>
+        <v>45281130660</v>
       </c>
       <c r="P3" t="n">
-        <v>22450</v>
+        <v>10360</v>
       </c>
       <c r="Q3" t="n">
-        <v>1760</v>
+        <v>2965</v>
       </c>
       <c r="R3" t="n">
-        <v>56000</v>
+        <v>-77000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>차세대 광반도체, 광통신 관련주로 부각되며 프로그램 및 주포의 매수세 유입 기대. 3분봉 패턴 및 거래량 증가 확인, 매물대 돌파 시도.</t>
+          <t>AI 보안 및 딥페이크 관련주로 언급되나, 차익 실현 매물 및 단기 급등 가능성에 대한 경계 심리 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', '매물대']</t>
+          <t>['AI 보안', '딥페이크', '단기 급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8780</v>
+        <v>8750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+11.00%</t>
+          <t>+10.62%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
         <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>53706627830</v>
+        <v>55209053465</v>
       </c>
       <c r="P4" t="n">
         <v>25050</v>
@@ -803,7 +803,7 @@
         <v>3705</v>
       </c>
       <c r="R4" t="n">
-        <v>16000</v>
+        <v>-24000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -854,13 +854,13 @@
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H5" t="n">
         <v>0.83</v>
@@ -886,7 +886,7 @@
         <v>0.82</v>
       </c>
       <c r="O5" t="n">
-        <v>29334052775</v>
+        <v>29767936005</v>
       </c>
       <c r="P5" t="n">
         <v>12800</v>
@@ -895,10 +895,10 @@
         <v>5340</v>
       </c>
       <c r="R5" t="n">
-        <v>353000</v>
+        <v>447000</v>
       </c>
       <c r="S5" t="n">
-        <v>99000</v>
+        <v>127000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2860</v>
+        <v>2825</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+9.16%</t>
+          <t>+7.82%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-2.39</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="H6" t="n">
         <v>1.44</v>
@@ -978,7 +978,7 @@
         <v>3.83</v>
       </c>
       <c r="O6" t="n">
-        <v>85971339375</v>
+        <v>86672739820</v>
       </c>
       <c r="P6" t="n">
         <v>4810</v>
@@ -987,7 +987,7 @@
         <v>1400</v>
       </c>
       <c r="R6" t="n">
-        <v>-309000</v>
+        <v>-240000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17000</v>
+        <v>17010</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+5.85%</t>
+          <t>+5.92%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G7" t="n">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="H7" t="n">
         <v>2.7</v>
@@ -1070,7 +1070,7 @@
         <v>2.39</v>
       </c>
       <c r="O7" t="n">
-        <v>235205040190</v>
+        <v>236922850330</v>
       </c>
       <c r="P7" t="n">
         <v>30550</v>
@@ -1079,23 +1079,23 @@
         <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>-135000</v>
+        <v>-292000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론에 대한 언급과 함께 주가 상승에 대한 기대감이 일부 존재함.</t>
+          <t>AI 개발 속도 조절론 관련주로 언급되며, 급락장 속에서도 강한 흐름을 기대하는 의견이 있으나 매물대 정리 및 주가 변동성이 관찰됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '속도 조절론']</t>
+          <t>['AI', '속도 조절론', '매물대']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3985</v>
+        <v>4070</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+2.97%</t>
+          <t>+5.17%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.45</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H8" t="n">
         <v>0.59</v>
@@ -1162,7 +1162,7 @@
         <v>1.04</v>
       </c>
       <c r="O8" t="n">
-        <v>67683368223</v>
+        <v>71032424657</v>
       </c>
       <c r="P8" t="n">
         <v>8100</v>
@@ -1171,7 +1171,7 @@
         <v>592</v>
       </c>
       <c r="R8" t="n">
-        <v>-153000</v>
+        <v>-217000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14380</v>
+        <v>14460</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>+2.19%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H9" t="n">
         <v>1.88</v>
@@ -1254,7 +1254,7 @@
         <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>69052070490</v>
+        <v>72102879050</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1263,10 +1263,10 @@
         <v>1272</v>
       </c>
       <c r="R9" t="n">
-        <v>-356000</v>
+        <v>-430000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14650</v>
+        <v>14670</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-1.97</v>
       </c>
       <c r="E10" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F10" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G10" t="n">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="H10" t="n">
         <v>1.17</v>
@@ -1346,7 +1346,7 @@
         <v>3.14</v>
       </c>
       <c r="O10" t="n">
-        <v>92855045385</v>
+        <v>94157274670</v>
       </c>
       <c r="P10" t="n">
         <v>36200</v>
@@ -1355,7 +1355,7 @@
         <v>8920</v>
       </c>
       <c r="R10" t="n">
-        <v>-23000</v>
+        <v>-128000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8290</v>
+        <v>8240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="F11" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G11" t="n">
-        <v>680</v>
+        <v>710</v>
       </c>
       <c r="H11" t="n">
         <v>0.75</v>
@@ -1438,7 +1438,7 @@
         <v>1.29</v>
       </c>
       <c r="O11" t="n">
-        <v>19121180510</v>
+        <v>19632032670</v>
       </c>
       <c r="P11" t="n">
         <v>21500</v>
@@ -1447,23 +1447,23 @@
         <v>2300</v>
       </c>
       <c r="R11" t="n">
-        <v>77000</v>
+        <v>64000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>페니트리움바이오, ‘가짜내성’ 타깃 항암 전략 제시로 글로벌 심포지엄 개최. 암 치료 신약 관련 기대감 형성.</t>
+          <t>항암 신약 개발 및 글로벌 심포지엄 개최 등 재료가 부각되며, 목표가 30만원 제시와 함께 상승 기대감이 형성되고 있으나 임상 결과에 대한 불확실성도 존재함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['항암 전략', '글로벌 심포지엄', '암 치료']</t>
+          <t>['항암 신약', '임상 결과', '목표가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1851</v>
+        <v>1854</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.36</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F12" t="n">
         <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H12" t="n">
         <v>2.08</v>
@@ -1530,7 +1530,7 @@
         <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>13741767917</v>
+        <v>13914552692</v>
       </c>
       <c r="P12" t="n">
         <v>4795</v>
@@ -1539,7 +1539,7 @@
         <v>1524</v>
       </c>
       <c r="R12" t="n">
-        <v>-192000</v>
+        <v>-224000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1575,184 +1575,184 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12040</v>
+        <v>89000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>-1.98%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.72</v>
+        <v>-0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>51</v>
+        <v>175</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="G13" t="n">
-        <v>39</v>
+        <v>559</v>
       </c>
       <c r="H13" t="n">
-        <v>0.22</v>
+        <v>23.56</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12290</v>
+        <v>90800</v>
       </c>
       <c r="K13" t="n">
-        <v>12030</v>
+        <v>89800</v>
       </c>
       <c r="L13" t="n">
-        <v>13230</v>
+        <v>90400</v>
       </c>
       <c r="M13" t="n">
-        <v>11820</v>
+        <v>87700</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9399999999999999</v>
+        <v>23.59</v>
       </c>
       <c r="O13" t="n">
-        <v>51670283715</v>
+        <v>131109671400</v>
       </c>
       <c r="P13" t="n">
-        <v>20850</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>4020</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>30000</v>
+        <v>-464000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-70000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>원전주 전반의 하락세 및 재료 소멸 가능성 언급, 보유 물량 관리 및 신규 진입에 대한 보수적 관점.</t>
+          <t>국제 유가 상승에 따른 원전주 상승 가능성과 기관 매집 정황이 있으나, 저항 매물대 및 단기 예상가에 대한 언급이 있어 상승 모멘텀은 제한적임.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전주', '폭락', '재료 소멸']</t>
+          <t>['국제 유가', '원전주', '기관 매집']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>88500</v>
+        <v>12015</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>-2.24%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.03</v>
+        <v>-0.72</v>
       </c>
       <c r="E14" t="n">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="F14" t="n">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="G14" t="n">
-        <v>556</v>
+        <v>37</v>
       </c>
       <c r="H14" t="n">
-        <v>23.56</v>
+        <v>0.22</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>90800</v>
+        <v>12290</v>
       </c>
       <c r="K14" t="n">
-        <v>89800</v>
+        <v>12030</v>
       </c>
       <c r="L14" t="n">
-        <v>90400</v>
+        <v>13230</v>
       </c>
       <c r="M14" t="n">
-        <v>87700</v>
+        <v>11820</v>
       </c>
       <c r="N14" t="n">
-        <v>23.59</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>126208240150</v>
+        <v>52072397265</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>20850</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>4020</v>
       </c>
       <c r="R14" t="n">
-        <v>-320000</v>
+        <v>2000</v>
       </c>
       <c r="S14" t="n">
-        <v>-89000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>국제 유가 상승에 따른 원전주 상승 가능성 및 기관의 매집 정황에 대한 기대감이 나타남.</t>
+          <t>원전주 전반의 하락세 및 재료 소멸 가능성 언급, 보유 물량 관리 및 신규 진입에 대한 보수적 관점.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['국제 유가', '원전주']</t>
+          <t>['원전주', '폭락', '재료 소멸']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>252000</v>
+        <v>253000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-2.50%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G15" t="n">
-        <v>1734</v>
+        <v>1756</v>
       </c>
       <c r="H15" t="n">
         <v>46.64</v>
@@ -1797,7 +1797,7 @@
         <v>249500</v>
       </c>
       <c r="L15" t="n">
-        <v>252500</v>
+        <v>253500</v>
       </c>
       <c r="M15" t="n">
         <v>249000</v>
@@ -1806,7 +1806,7 @@
         <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>1703128865500</v>
+        <v>1811109635750</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1815,23 +1815,23 @@
         <v>75900</v>
       </c>
       <c r="R15" t="n">
-        <v>-1189000</v>
+        <v>-2179000</v>
       </c>
       <c r="S15" t="n">
-        <v>-852000</v>
+        <v>-1014000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 언급이 주를 이루며, 주가 하락에 대한 우려가 제기됨.</t>
+          <t>정치적 이슈와 연관되어 부정적인 전망이 다수이며, 주가 하락에 대한 불만과 함께 '30전자' 언급 등 기대감은 낮음.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['주가 하락', '정치적 이슈', '기대감']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19090</v>
+        <v>19100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G16" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H16" t="n">
         <v>10.55</v>
@@ -1898,7 +1898,7 @@
         <v>10.65</v>
       </c>
       <c r="O16" t="n">
-        <v>44081248205</v>
+        <v>45659664095</v>
       </c>
       <c r="P16" t="n">
         <v>40350</v>
@@ -1907,10 +1907,10 @@
         <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>-224000</v>
+        <v>-430000</v>
       </c>
       <c r="S16" t="n">
-        <v>5000</v>
+        <v>-48000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1733000</v>
+        <v>1736000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-4.19%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G17" t="n">
-        <v>1175</v>
+        <v>1221</v>
       </c>
       <c r="H17" t="n">
         <v>50.47</v>
@@ -1981,7 +1981,7 @@
         <v>1707000</v>
       </c>
       <c r="L17" t="n">
-        <v>1734000</v>
+        <v>1740000</v>
       </c>
       <c r="M17" t="n">
         <v>1695000</v>
@@ -1990,7 +1990,7 @@
         <v>50.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3197361413000</v>
+        <v>3354586989000</v>
       </c>
       <c r="P17" t="n">
         <v>2987000</v>
@@ -1999,14 +1999,14 @@
         <v>325000</v>
       </c>
       <c r="R17" t="n">
-        <v>-662000</v>
+        <v>-897000</v>
       </c>
       <c r="S17" t="n">
-        <v>-142000</v>
+        <v>-147000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>금리 인상, 정부 정책에 대한 부정적 언급과 함께 주가 하락에 대한 우려가 제기됨. 외인 매도세에 대한 언급이 일부 있음.</t>
+          <t>공매도 금지 요청 및 주가 하락에 대한 불안감이 크며, 정부 정책 및 시장 상황에 대한 불만이 제기되고 반등에 대한 의구심이 존재함.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['금리 인상', '외인 매도']</t>
+          <t>['공매도', '주가 하락', '시장 상황']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11870</v>
+        <v>11830</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.66%</t>
+          <t>-4.98%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.51</v>
       </c>
       <c r="E18" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H18" t="n">
         <v>17.58</v>
@@ -2082,7 +2082,7 @@
         <v>17.07</v>
       </c>
       <c r="O18" t="n">
-        <v>52471192750</v>
+        <v>53205699540</v>
       </c>
       <c r="P18" t="n">
         <v>14350</v>
@@ -2091,7 +2091,7 @@
         <v>465</v>
       </c>
       <c r="R18" t="n">
-        <v>69000</v>
+        <v>-51000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>23757311125</v>
+        <v>24020258185</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
@@ -2183,7 +2183,7 @@
         <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>-63000</v>
+        <v>-67000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260914_11.xlsx
+++ b/data/trending_integrated_20260914_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9670</v>
+        <v>9690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+22.41%</t>
+          <t>+22.66%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G2" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>185344869450</v>
+        <v>193794113840</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 관련주로, SK하이닉스 CPO 광원 이슈와 함께 3분봉 기반 매물대 돌파 및 전고점 돌파 기대감이 높음.</t>
+          <t>차세대 광반도체 및 광통신 관련주로 주목받으며, 3분봉상 매물대 돌파 및 SK하이닉스 CPO 광원 이슈로 강한 상승 흐름.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6710</v>
+        <v>6660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+21.78%</t>
+          <t>+20.87%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>45281130660</v>
+        <v>45950620085</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8750</v>
+        <v>9130</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.62%</t>
+          <t>+10.13%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.55</v>
+        <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>64</v>
+        <v>162</v>
       </c>
       <c r="H4" t="n">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7910</v>
+        <v>8290</v>
       </c>
       <c r="K4" t="n">
-        <v>7800</v>
+        <v>8300</v>
       </c>
       <c r="L4" t="n">
-        <v>9840</v>
+        <v>9425</v>
       </c>
       <c r="M4" t="n">
-        <v>7540</v>
+        <v>8300</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="O4" t="n">
-        <v>55209053465</v>
+        <v>30025734420</v>
       </c>
       <c r="P4" t="n">
-        <v>25050</v>
+        <v>12800</v>
       </c>
       <c r="Q4" t="n">
-        <v>3705</v>
+        <v>5340</v>
       </c>
       <c r="R4" t="n">
-        <v>-24000</v>
+        <v>447000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
+          <t>폴더블폰 시장 확대에 따른 수혜 기대감, 그러나 단기 차익 실현 및 전환사채 관련 이슈로 인한 변동성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['펩타이드', '특허 등록', '면역 조절']</t>
+          <t>['폴더블', '매출 증', '전환사채']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>441270</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9150</v>
+        <v>8620</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+10.37%</t>
+          <t>+8.98%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01</v>
+        <v>0.55</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>159</v>
+        <v>66</v>
       </c>
       <c r="H5" t="n">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8290</v>
+        <v>7910</v>
       </c>
       <c r="K5" t="n">
-        <v>8300</v>
+        <v>7800</v>
       </c>
       <c r="L5" t="n">
-        <v>9425</v>
+        <v>9840</v>
       </c>
       <c r="M5" t="n">
-        <v>8300</v>
+        <v>7540</v>
       </c>
       <c r="N5" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>29767936005</v>
+        <v>56388071345</v>
       </c>
       <c r="P5" t="n">
-        <v>12800</v>
+        <v>25050</v>
       </c>
       <c r="Q5" t="n">
-        <v>5340</v>
+        <v>3705</v>
       </c>
       <c r="R5" t="n">
-        <v>447000</v>
+        <v>-24000</v>
       </c>
       <c r="S5" t="n">
-        <v>127000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>폴더블폰 시장 확대에 따른 수혜 기대감, 그러나 단기 차익 실현 및 전환사채 관련 이슈로 인한 변동성.</t>
+          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['폴더블', '매출 증', '전환사채']</t>
+          <t>['펩타이드', '특허 등록', '면역 조절']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2825</v>
+        <v>2810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+7.82%</t>
+          <t>+7.25%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-2.39</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H6" t="n">
         <v>1.44</v>
@@ -978,7 +978,7 @@
         <v>3.83</v>
       </c>
       <c r="O6" t="n">
-        <v>86672739820</v>
+        <v>87693364352</v>
       </c>
       <c r="P6" t="n">
         <v>4810</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17010</v>
+        <v>4090</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+5.92%</t>
+          <t>+5.68%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.31</v>
+        <v>-0.45</v>
       </c>
       <c r="E7" t="n">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>0.59</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16060</v>
+        <v>3870</v>
       </c>
       <c r="K7" t="n">
-        <v>16780</v>
+        <v>3860</v>
       </c>
       <c r="L7" t="n">
-        <v>18610</v>
+        <v>4135</v>
       </c>
       <c r="M7" t="n">
-        <v>16230</v>
+        <v>3740</v>
       </c>
       <c r="N7" t="n">
-        <v>2.39</v>
+        <v>1.04</v>
       </c>
       <c r="O7" t="n">
-        <v>236922850330</v>
+        <v>74242880152</v>
       </c>
       <c r="P7" t="n">
-        <v>30550</v>
+        <v>8100</v>
       </c>
       <c r="Q7" t="n">
-        <v>6100</v>
+        <v>592</v>
       </c>
       <c r="R7" t="n">
-        <v>-292000</v>
+        <v>-217000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론 관련주로 언급되며, 급락장 속에서도 강한 흐름을 기대하는 의견이 있으나 매물대 정리 및 주가 변동성이 관찰됨.</t>
+          <t>GPU, 광통신, AIDC 관련 기술 성장 기대감 속에 주가 상승. 프로그램 매수세 유입 및 추세적 상승 전망, 4150원 평단가 대비 목표가 7500원 제시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '속도 조절론', '매물대']</t>
+          <t>['광통신', 'AIDC', '추세적 상승']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4070</v>
+        <v>16940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.17%</t>
+          <t>+5.48%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.45</v>
+        <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="G8" t="n">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="H8" t="n">
-        <v>0.59</v>
+        <v>2.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3870</v>
+        <v>16060</v>
       </c>
       <c r="K8" t="n">
-        <v>3860</v>
+        <v>16780</v>
       </c>
       <c r="L8" t="n">
-        <v>4135</v>
+        <v>18610</v>
       </c>
       <c r="M8" t="n">
-        <v>3740</v>
+        <v>16230</v>
       </c>
       <c r="N8" t="n">
-        <v>1.04</v>
+        <v>2.39</v>
       </c>
       <c r="O8" t="n">
-        <v>71032424657</v>
+        <v>238386967965</v>
       </c>
       <c r="P8" t="n">
-        <v>8100</v>
+        <v>30550</v>
       </c>
       <c r="Q8" t="n">
-        <v>592</v>
+        <v>6100</v>
       </c>
       <c r="R8" t="n">
-        <v>-217000</v>
+        <v>-292000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>GPU, 광통신, AIDC 관련 기술 성장 기대감 속에 주가 상승. 프로그램 매수세 유입 및 추세적 상승 전망, 4150원 평단가 대비 목표가 7500원 제시.</t>
+          <t>AI 개발 속도 조절론과 양자 보안 테마 연관, 급락장 속에서도 강한 흐름을 보이며 매물대 돌파 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', '추세적 상승']</t>
+          <t>['AI', '양자보안', '매물대']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14460</v>
+        <v>14450</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+2.19%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>97</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G9" t="n">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="H9" t="n">
         <v>1.88</v>
@@ -1254,7 +1254,7 @@
         <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>72102879050</v>
+        <v>73978440810</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>GPU 확보 및 AIDC 광통신 기술 투자 확대 뉴스에 기반한 주가 상승 기대감이 나타남. 금리 동결 가능성에 대한 언급도 있음.</t>
+          <t>AIDC 광통신 기술 성장 및 GPU 확보 관련 수혜 전망, 광전자와 함께 광통신 테마 내 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', 'GPU']</t>
+          <t>['광통신', 'AIDC', 'GPU']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14670</v>
+        <v>14690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-1.97</v>
       </c>
       <c r="E10" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F10" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G10" t="n">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="H10" t="n">
         <v>1.17</v>
@@ -1346,7 +1346,7 @@
         <v>3.14</v>
       </c>
       <c r="O10" t="n">
-        <v>94157274670</v>
+        <v>94711810145</v>
       </c>
       <c r="P10" t="n">
         <v>36200</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>이란-걸프국가 회담 연기 소식과 국제 유가 상승에 따른 주가 상승 기대감이 나타남. 외인, 기관 매도세에 대한 언급도 있음.</t>
+          <t>이란-걸프국가 회담 연기 및 국제 유가 폭등 관련 수혜 기대, 외인·기관 매도세에도 불구하고 유가 상승 모멘텀으로 인한 상승 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['국제 유가', '호르무즈 해협']</t>
+          <t>['국제유가', '흥구석유', '호르무즈']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8240</v>
+        <v>8250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F11" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G11" t="n">
-        <v>710</v>
+        <v>742</v>
       </c>
       <c r="H11" t="n">
         <v>0.75</v>
@@ -1438,7 +1438,7 @@
         <v>1.29</v>
       </c>
       <c r="O11" t="n">
-        <v>19632032670</v>
+        <v>19886937440</v>
       </c>
       <c r="P11" t="n">
         <v>21500</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H12" t="n">
         <v>2.08</v>
@@ -1530,7 +1530,7 @@
         <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>13914552692</v>
+        <v>14031367756</v>
       </c>
       <c r="P12" t="n">
         <v>4795</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>89000</v>
+        <v>88900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.98%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F13" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G13" t="n">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="H13" t="n">
         <v>23.56</v>
@@ -1622,7 +1622,7 @@
         <v>23.59</v>
       </c>
       <c r="O13" t="n">
-        <v>131109671400</v>
+        <v>134322302000</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국제 유가 상승에 따른 원전주 상승 가능성과 기관 매집 정황이 있으나, 저항 매물대 및 단기 예상가에 대한 언급이 있어 상승 모멘텀은 제한적임.</t>
+          <t>국제 유가 상승 시 원전주 상승 가능성 언급, 9만원대 방어를 통한 기관 매수세 유입 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['국제 유가', '원전주', '기관 매집']</t>
+          <t>['원전주', '국제유가', '기관매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,184 +1667,184 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12015</v>
+        <v>253000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.24%</t>
+          <t>-2.50%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.72</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>51</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>505</v>
       </c>
       <c r="G14" t="n">
-        <v>37</v>
+        <v>1705</v>
       </c>
       <c r="H14" t="n">
-        <v>0.22</v>
+        <v>46.64</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>12290</v>
+        <v>259500</v>
       </c>
       <c r="K14" t="n">
-        <v>12030</v>
+        <v>249500</v>
       </c>
       <c r="L14" t="n">
-        <v>13230</v>
+        <v>253500</v>
       </c>
       <c r="M14" t="n">
-        <v>11820</v>
+        <v>249000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9399999999999999</v>
+        <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>52072397265</v>
+        <v>1899355203000</v>
       </c>
       <c r="P14" t="n">
-        <v>20850</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>4020</v>
+        <v>75900</v>
       </c>
       <c r="R14" t="n">
-        <v>2000</v>
+        <v>-2179000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-1014000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>원전주 전반의 하락세 및 재료 소멸 가능성 언급, 보유 물량 관리 및 신규 진입에 대한 보수적 관점.</t>
+          <t>정치적 이슈와 연계된 부정적 전망 다수, HBM 개발 지연 가능성 및 전반적인 국내 증시 상황으로 인한 하락 위기 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전주', '폭락', '재료 소멸']</t>
+          <t>['정치이슈', 'HBM', '하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>253000</v>
+        <v>11980</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.50%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.72</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>513</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>1756</v>
+        <v>38</v>
       </c>
       <c r="H15" t="n">
-        <v>46.64</v>
+        <v>0.22</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>259500</v>
+        <v>12290</v>
       </c>
       <c r="K15" t="n">
-        <v>249500</v>
+        <v>12030</v>
       </c>
       <c r="L15" t="n">
-        <v>253500</v>
+        <v>13230</v>
       </c>
       <c r="M15" t="n">
-        <v>249000</v>
+        <v>11820</v>
       </c>
       <c r="N15" t="n">
-        <v>46.71</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>1811109635750</v>
+        <v>52550158150</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>20850</v>
       </c>
       <c r="Q15" t="n">
-        <v>75900</v>
+        <v>4020</v>
       </c>
       <c r="R15" t="n">
-        <v>-2179000</v>
+        <v>2000</v>
       </c>
       <c r="S15" t="n">
-        <v>-1014000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관되어 부정적인 전망이 다수이며, 주가 하락에 대한 불만과 함께 '30전자' 언급 등 기대감은 낮음.</t>
+          <t>원전주 전반의 하락세 및 재료 소멸 가능성 언급, 보유 물량 관리 및 신규 진입에 대한 보수적 관점.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 하락', '정치적 이슈', '기대감']</t>
+          <t>['원전주', '폭락', '재료 소멸']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19100</v>
+        <v>19110</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.97%</t>
+          <t>-3.92%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G16" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H16" t="n">
         <v>10.55</v>
@@ -1898,7 +1898,7 @@
         <v>10.65</v>
       </c>
       <c r="O16" t="n">
-        <v>45659664095</v>
+        <v>46860945995</v>
       </c>
       <c r="P16" t="n">
         <v>40350</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1736000</v>
+        <v>1734000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.19%</t>
+          <t>-4.30%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="G17" t="n">
-        <v>1221</v>
+        <v>1244</v>
       </c>
       <c r="H17" t="n">
         <v>50.47</v>
@@ -1990,7 +1990,7 @@
         <v>50.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3354586989000</v>
+        <v>3448078780500</v>
       </c>
       <c r="P17" t="n">
         <v>2987000</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>공매도 금지 요청 및 주가 하락에 대한 불안감이 크며, 정부 정책 및 시장 상황에 대한 불만이 제기되고 반등에 대한 의구심이 존재함.</t>
+          <t>금리 인상 우려 및 정치적 이슈로 인한 하락세 지속, 170만원 및 150만원 이하로의 추가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도', '주가 하락', '시장 상황']</t>
+          <t>['금리인상', '하락', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11830</v>
+        <v>11870</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.98%</t>
+          <t>-4.66%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.51</v>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F18" t="n">
         <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H18" t="n">
         <v>17.58</v>
@@ -2082,7 +2082,7 @@
         <v>17.07</v>
       </c>
       <c r="O18" t="n">
-        <v>53205699540</v>
+        <v>53653820590</v>
       </c>
       <c r="P18" t="n">
         <v>14350</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13940</v>
+        <v>14020</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G19" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>24020258185</v>
+        <v>24284683000</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>

--- a/data/trending_integrated_20260914_11.xlsx
+++ b/data/trending_integrated_20260914_11.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9690</v>
+        <v>9770</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+22.66%</t>
+          <t>+23.67%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>93</v>
       </c>
       <c r="F2" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -601,7 +601,7 @@
         <v>7790</v>
       </c>
       <c r="L2" t="n">
-        <v>9710</v>
+        <v>9850</v>
       </c>
       <c r="M2" t="n">
         <v>7700</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>193794113840</v>
+        <v>207925064875</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 관련주로 주목받으며, 3분봉상 매물대 돌파 및 SK하이닉스 CPO 광원 이슈로 강한 상승 흐름.</t>
+          <t>차세대 광반도체 및 광통신 관련주로, SK하이닉스 CPO 광원 이슈에 따른 급등 기대감. 단기 매물대 돌파 및 주포/프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6660</v>
+        <v>6630</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+20.87%</t>
+          <t>+20.33%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
         <v>81</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>45950620085</v>
+        <v>46490343935</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9130</v>
+        <v>9190</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.13%</t>
+          <t>+10.86%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H4" t="n">
         <v>0.83</v>
@@ -794,7 +794,7 @@
         <v>0.82</v>
       </c>
       <c r="O4" t="n">
-        <v>30025734420</v>
+        <v>30424842110</v>
       </c>
       <c r="P4" t="n">
         <v>12800</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8620</v>
+        <v>8600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+8.98%</t>
+          <t>+8.72%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.55</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
         <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H5" t="n">
         <v>1.25</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>56388071345</v>
+        <v>56995478820</v>
       </c>
       <c r="P5" t="n">
         <v>25050</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2810</v>
+        <v>4145</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+7.25%</t>
+          <t>+7.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.39</v>
+        <v>-0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="H6" t="n">
-        <v>1.44</v>
+        <v>0.59</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2620</v>
+        <v>3870</v>
       </c>
       <c r="K6" t="n">
-        <v>2745</v>
+        <v>3860</v>
       </c>
       <c r="L6" t="n">
-        <v>3145</v>
+        <v>4185</v>
       </c>
       <c r="M6" t="n">
-        <v>2700</v>
+        <v>3740</v>
       </c>
       <c r="N6" t="n">
-        <v>3.83</v>
+        <v>1.04</v>
       </c>
       <c r="O6" t="n">
-        <v>87693364352</v>
+        <v>89582967976</v>
       </c>
       <c r="P6" t="n">
-        <v>4810</v>
+        <v>8100</v>
       </c>
       <c r="Q6" t="n">
-        <v>1400</v>
+        <v>592</v>
       </c>
       <c r="R6" t="n">
-        <v>-240000</v>
+        <v>-217000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>양자 보안 관련주로 부각되며 강한 상승세 시현. 매출액 및 영업이익 증가 추세, 4800원 전고점 돌파 기대. 투경 조건 진입 시 매도 권고.</t>
+          <t>GPU, 광통신, AIDC 관련 기술 성장 기대감 속에 주가 상승. 프로그램 매수세 유입 및 추세적 상승 전망, 4150원 평단가 대비 목표가 7500원 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['양자 보안', '매출액', '전고점 돌파']</t>
+          <t>['광통신', 'AIDC', '추세적 상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4090</v>
+        <v>2790</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+5.68%</t>
+          <t>+6.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.45</v>
+        <v>-2.39</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="H7" t="n">
-        <v>0.59</v>
+        <v>1.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3870</v>
+        <v>2620</v>
       </c>
       <c r="K7" t="n">
-        <v>3860</v>
+        <v>2745</v>
       </c>
       <c r="L7" t="n">
-        <v>4135</v>
+        <v>3145</v>
       </c>
       <c r="M7" t="n">
-        <v>3740</v>
+        <v>2700</v>
       </c>
       <c r="N7" t="n">
-        <v>1.04</v>
+        <v>3.83</v>
       </c>
       <c r="O7" t="n">
-        <v>74242880152</v>
+        <v>88807964225</v>
       </c>
       <c r="P7" t="n">
-        <v>8100</v>
+        <v>4810</v>
       </c>
       <c r="Q7" t="n">
-        <v>592</v>
+        <v>1400</v>
       </c>
       <c r="R7" t="n">
-        <v>-217000</v>
+        <v>-240000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>GPU, 광통신, AIDC 관련 기술 성장 기대감 속에 주가 상승. 프로그램 매수세 유입 및 추세적 상승 전망, 4150원 평단가 대비 목표가 7500원 제시.</t>
+          <t>양자 보안 관련주로 부각되며 강한 상승세 시현. 매출액 및 영업이익 증가 추세, 4800원 전고점 돌파 기대. 투경 조건 진입 시 매도 권고.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', '추세적 상승']</t>
+          <t>['양자 보안', '매출액', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F8" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G8" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H8" t="n">
         <v>2.7</v>
@@ -1162,7 +1162,7 @@
         <v>2.39</v>
       </c>
       <c r="O8" t="n">
-        <v>238386967965</v>
+        <v>240429113815</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14450</v>
+        <v>14580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+2.12%</t>
+          <t>+3.04%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9" t="n">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="H9" t="n">
         <v>1.88</v>
@@ -1245,7 +1245,7 @@
         <v>13850</v>
       </c>
       <c r="L9" t="n">
-        <v>14530</v>
+        <v>14660</v>
       </c>
       <c r="M9" t="n">
         <v>13800</v>
@@ -1254,7 +1254,7 @@
         <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>73978440810</v>
+        <v>83513649615</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AIDC 광통신 기술 성장 및 GPU 확보 관련 수혜 전망, 광전자와 함께 광통신 테마 내 대장주 역할 기대.</t>
+          <t>AI 가속화에 따른 AIDC 광통신 기술 성장 전망. GPU 확보 후 '연결' 중요성 부각. 대한광통신 기술력 및 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14690</v>
+        <v>8250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.97</v>
+        <v>-0.54</v>
       </c>
       <c r="E10" t="n">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="F10" t="n">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="G10" t="n">
-        <v>561</v>
+        <v>775</v>
       </c>
       <c r="H10" t="n">
-        <v>1.17</v>
+        <v>0.75</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14610</v>
+        <v>8290</v>
       </c>
       <c r="K10" t="n">
-        <v>15420</v>
+        <v>8100</v>
       </c>
       <c r="L10" t="n">
-        <v>16510</v>
+        <v>9050</v>
       </c>
       <c r="M10" t="n">
-        <v>14540</v>
+        <v>8060</v>
       </c>
       <c r="N10" t="n">
-        <v>3.14</v>
+        <v>1.29</v>
       </c>
       <c r="O10" t="n">
-        <v>94711810145</v>
+        <v>20230671625</v>
       </c>
       <c r="P10" t="n">
-        <v>36200</v>
+        <v>21500</v>
       </c>
       <c r="Q10" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R10" t="n">
-        <v>-128000</v>
+        <v>64000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>이란-걸프국가 회담 연기 및 국제 유가 폭등 관련 수혜 기대, 외인·기관 매도세에도 불구하고 유가 상승 모멘텀으로 인한 상승 전망.</t>
+          <t>암 치료 바이오 신약 관련주로, '가짜내성' 타깃 항암 전략 제시. 글로벌 심포지엄 개최 및 탑급 교수 발표. 재료 핵폭탄급, 낮은 시총 기반 급등 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['국제유가', '흥구석유', '호르무즈']</t>
+          <t>['항암', '바이오신약', '심포지엄']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8250</v>
+        <v>14350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.78%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.54</v>
+        <v>-1.97</v>
       </c>
       <c r="E11" t="n">
-        <v>124</v>
+        <v>228</v>
       </c>
       <c r="F11" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="G11" t="n">
-        <v>742</v>
+        <v>592</v>
       </c>
       <c r="H11" t="n">
-        <v>0.75</v>
+        <v>1.17</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8290</v>
+        <v>14610</v>
       </c>
       <c r="K11" t="n">
-        <v>8100</v>
+        <v>15420</v>
       </c>
       <c r="L11" t="n">
-        <v>9050</v>
+        <v>16510</v>
       </c>
       <c r="M11" t="n">
-        <v>8060</v>
+        <v>14320</v>
       </c>
       <c r="N11" t="n">
-        <v>1.29</v>
+        <v>3.14</v>
       </c>
       <c r="O11" t="n">
-        <v>19886937440</v>
+        <v>97107241675</v>
       </c>
       <c r="P11" t="n">
-        <v>21500</v>
+        <v>36200</v>
       </c>
       <c r="Q11" t="n">
-        <v>2300</v>
+        <v>8920</v>
       </c>
       <c r="R11" t="n">
-        <v>64000</v>
+        <v>-128000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>항암 신약 개발 및 글로벌 심포지엄 개최 등 재료가 부각되며, 목표가 30만원 제시와 함께 상승 기대감이 형성되고 있으나 임상 결과에 대한 불확실성도 존재함.</t>
+          <t>이란-걸프국가 호르무즈 해협 회담 연기 및 국제 유가 폭등 관련주. 브렌트유 최고점, WTI 104달러 돌파 직전 상황. 외인, 기관, 프로그램 동반 매도 중.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['항암 신약', '임상 결과', '목표가']</t>
+          <t>['국제유가', '호르무즈', '회담연기']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1856</v>
+        <v>1843</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.36</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
         <v>194</v>
@@ -1524,13 +1524,13 @@
         <v>1961</v>
       </c>
       <c r="M12" t="n">
-        <v>1848</v>
+        <v>1840</v>
       </c>
       <c r="N12" t="n">
         <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>14031367756</v>
+        <v>14350975893</v>
       </c>
       <c r="P12" t="n">
         <v>4795</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>88900</v>
+        <v>88850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>-2.15%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F13" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G13" t="n">
-        <v>566</v>
+        <v>581</v>
       </c>
       <c r="H13" t="n">
         <v>23.56</v>
@@ -1622,7 +1622,7 @@
         <v>23.59</v>
       </c>
       <c r="O13" t="n">
-        <v>134322302000</v>
+        <v>136173954300</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253000</v>
+        <v>253750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.50%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="G14" t="n">
-        <v>1705</v>
+        <v>1733</v>
       </c>
       <c r="H14" t="n">
         <v>46.64</v>
@@ -1705,7 +1705,7 @@
         <v>249500</v>
       </c>
       <c r="L14" t="n">
-        <v>253500</v>
+        <v>254000</v>
       </c>
       <c r="M14" t="n">
         <v>249000</v>
@@ -1714,7 +1714,7 @@
         <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>1899355203000</v>
+        <v>1980152160250</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11980</v>
+        <v>11920</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-3.01%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.72</v>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
         <v>38</v>
@@ -1806,7 +1806,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>52550158150</v>
+        <v>52822907595</v>
       </c>
       <c r="P15" t="n">
         <v>20850</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19110</v>
+        <v>1736000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.92%</t>
+          <t>-4.19%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>524</v>
       </c>
       <c r="G16" t="n">
-        <v>254</v>
+        <v>1275</v>
       </c>
       <c r="H16" t="n">
-        <v>10.55</v>
+        <v>50.47</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>19890</v>
+        <v>1812000</v>
       </c>
       <c r="K16" t="n">
-        <v>19480</v>
+        <v>1707000</v>
       </c>
       <c r="L16" t="n">
-        <v>19550</v>
+        <v>1740000</v>
       </c>
       <c r="M16" t="n">
-        <v>18780</v>
+        <v>1695000</v>
       </c>
       <c r="N16" t="n">
-        <v>10.65</v>
+        <v>50.55</v>
       </c>
       <c r="O16" t="n">
-        <v>46860945995</v>
+        <v>3519549803500</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>325000</v>
       </c>
       <c r="R16" t="n">
-        <v>-430000</v>
+        <v>-897000</v>
       </c>
       <c r="S16" t="n">
-        <v>-48000</v>
+        <v>-147000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대차 해지 운동 및 공매도 세력과의 대립 구도 형성. 저점 매수 기회 및 주가 반등 기대감 언급, 투자자 참여 독려.</t>
+          <t>금리 인상 확정 시 불확실성 해소 기대. 외인 선물 매수 전환 및 175만원 회복 시 추세 회복 전망. 단기 하락 추세 및 150만원까지 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '반등 기대']</t>
+          <t>['금리인상', '외인매수', '추세회복']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1734000</v>
+        <v>19040</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.30%</t>
+          <t>-4.27%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>54</v>
       </c>
       <c r="F17" t="n">
-        <v>531</v>
+        <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>1244</v>
+        <v>268</v>
       </c>
       <c r="H17" t="n">
-        <v>50.47</v>
+        <v>10.55</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,91 +1975,91 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1812000</v>
+        <v>19890</v>
       </c>
       <c r="K17" t="n">
-        <v>1707000</v>
+        <v>19480</v>
       </c>
       <c r="L17" t="n">
-        <v>1740000</v>
+        <v>19550</v>
       </c>
       <c r="M17" t="n">
-        <v>1695000</v>
+        <v>18780</v>
       </c>
       <c r="N17" t="n">
-        <v>50.55</v>
+        <v>10.65</v>
       </c>
       <c r="O17" t="n">
-        <v>3448078780500</v>
+        <v>48061633310</v>
       </c>
       <c r="P17" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q17" t="n">
-        <v>325000</v>
+        <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>-897000</v>
+        <v>-430000</v>
       </c>
       <c r="S17" t="n">
-        <v>-147000</v>
+        <v>-48000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>금리 인상 우려 및 정치적 이슈로 인한 하락세 지속, 170만원 및 150만원 이하로의 추가 하락 가능성 언급.</t>
+          <t>대차 해지 운동 및 공매도 세력과의 대립 구도 형성. 저점 매수 기회 및 주가 반등 기대감 언급, 투자자 참여 독려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['금리인상', '하락', '공매도']</t>
+          <t>['대차 해지', '공매도', '반등 기대']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11870</v>
+        <v>13980</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.66%</t>
+          <t>-4.96%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="H18" t="n">
-        <v>17.58</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>12450</v>
+        <v>14710</v>
       </c>
       <c r="K18" t="n">
-        <v>11960</v>
+        <v>14710</v>
       </c>
       <c r="L18" t="n">
-        <v>13900</v>
+        <v>15420</v>
       </c>
       <c r="M18" t="n">
-        <v>11810</v>
+        <v>13700</v>
       </c>
       <c r="N18" t="n">
-        <v>17.07</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>53653820590</v>
+        <v>24573659895</v>
       </c>
       <c r="P18" t="n">
-        <v>14350</v>
+        <v>19380</v>
       </c>
       <c r="Q18" t="n">
-        <v>465</v>
+        <v>3200</v>
       </c>
       <c r="R18" t="n">
-        <v>-51000</v>
+        <v>-67000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>외국인 대량 매수세 유입되며 급등 기대감 형성. 단기 급등 후 주가 조정 및 변동성 확대, 수급 변화 주목.</t>
+          <t>수원 파장1구역 재건축 시공사 선정 소식에도 불구하고, 부동산 시장 침체 및 외인 매도세로 주가 하락. 1만원대 지지선 약화 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['외국인 매수', '급등 기대', '주가 변동성']</t>
+          <t>['재건축', '부동산 침체', '외인 매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14020</v>
+        <v>11830</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.69%</t>
+          <t>-4.98%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F19" t="n">
         <v>44</v>
       </c>
       <c r="G19" t="n">
-        <v>191</v>
+        <v>134</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>17.58</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14710</v>
+        <v>12450</v>
       </c>
       <c r="K19" t="n">
-        <v>14710</v>
+        <v>11960</v>
       </c>
       <c r="L19" t="n">
-        <v>15420</v>
+        <v>13900</v>
       </c>
       <c r="M19" t="n">
-        <v>13700</v>
+        <v>11800</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>17.07</v>
       </c>
       <c r="O19" t="n">
-        <v>24284683000</v>
+        <v>54437744560</v>
       </c>
       <c r="P19" t="n">
-        <v>19380</v>
+        <v>14350</v>
       </c>
       <c r="Q19" t="n">
-        <v>3200</v>
+        <v>465</v>
       </c>
       <c r="R19" t="n">
-        <v>-67000</v>
+        <v>-51000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>수원 파장1구역 재건축 시공사 선정 소식에도 불구하고, 부동산 시장 침체 및 외인 매도세로 주가 하락. 1만원대 지지선 약화 우려.</t>
+          <t>외국인 대량 매수세 유입되며 급등 기대감 형성. 단기 급등 후 주가 조정 및 변동성 확대, 수급 변화 주목.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['재건축', '부동산 침체', '외인 매도']</t>
+          <t>['외국인 매수', '급등 기대', '주가 변동성']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>001210</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260914_11.xlsx
+++ b/data/trending_integrated_20260914_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9770</v>
+        <v>9920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+23.67%</t>
+          <t>+25.57%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -601,7 +601,7 @@
         <v>7790</v>
       </c>
       <c r="L2" t="n">
-        <v>9850</v>
+        <v>9970</v>
       </c>
       <c r="M2" t="n">
         <v>7700</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>207925064875</v>
+        <v>220750858680</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 관련주로, SK하이닉스 CPO 광원 이슈에 따른 급등 기대감. 단기 매물대 돌파 및 주포/프로그램 매수세 유입.</t>
+          <t>차세대 광반도체 및 광통신 테마 상승 기대감. SK하이닉스 CPO 광원 관련 이슈 부각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6630</v>
+        <v>6510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+20.33%</t>
+          <t>+18.15%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
         <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>46490343935</v>
+        <v>47837793575</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9190</v>
+        <v>9140</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.86%</t>
+          <t>+10.25%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="H4" t="n">
         <v>0.83</v>
@@ -794,7 +794,7 @@
         <v>0.82</v>
       </c>
       <c r="O4" t="n">
-        <v>30424842110</v>
+        <v>30631662910</v>
       </c>
       <c r="P4" t="n">
         <v>12800</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8600</v>
+        <v>8670</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+8.72%</t>
+          <t>+9.61%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.55</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H5" t="n">
         <v>1.25</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>56995478820</v>
+        <v>59298170690</v>
       </c>
       <c r="P5" t="n">
         <v>25050</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4145</v>
+        <v>4210</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+7.11%</t>
+          <t>+8.79%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="H6" t="n">
         <v>0.59</v>
@@ -969,7 +969,7 @@
         <v>3860</v>
       </c>
       <c r="L6" t="n">
-        <v>4185</v>
+        <v>4285</v>
       </c>
       <c r="M6" t="n">
         <v>3740</v>
@@ -978,7 +978,7 @@
         <v>1.04</v>
       </c>
       <c r="O6" t="n">
-        <v>89582967976</v>
+        <v>108400494335</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2790</v>
+        <v>2775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.49%</t>
+          <t>+5.92%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-2.39</v>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H7" t="n">
         <v>1.44</v>
@@ -1070,7 +1070,7 @@
         <v>3.83</v>
       </c>
       <c r="O7" t="n">
-        <v>88807964225</v>
+        <v>89828146664</v>
       </c>
       <c r="P7" t="n">
         <v>4810</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16940</v>
+        <v>16760</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.48%</t>
+          <t>+4.36%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F8" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G8" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H8" t="n">
         <v>2.7</v>
@@ -1162,7 +1162,7 @@
         <v>2.39</v>
       </c>
       <c r="O8" t="n">
-        <v>240429113815</v>
+        <v>243632765620</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론과 양자 보안 테마 연관, 급락장 속에서도 강한 흐름을 보이며 매물대 돌파 기대.</t>
+          <t>AI 개발 속도 조절론 관련 논쟁 속 양자 보안 테마 기대감. 주가 변동성 속 매물대 정리.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14580</v>
+        <v>14650</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+3.04%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="H9" t="n">
         <v>1.88</v>
@@ -1239,28 +1239,28 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14150</v>
+        <v>14740</v>
       </c>
       <c r="K9" t="n">
-        <v>13850</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>14660</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>13800</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>83513649615</v>
+        <v>90132000000</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>-430000</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 가속화에 따른 AIDC 광통신 기술 성장 전망. GPU 확보 후 '연결' 중요성 부각. 대한광통신 기술력 및 프로그램 매수세 유입.</t>
+          <t>AIDC 및 광통신 기술 성장 전망. GPU 확보에 이은 연결성 강화 관련 긍정적 뉴스.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8250</v>
+        <v>8230</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.54</v>
       </c>
       <c r="E10" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F10" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G10" t="n">
-        <v>775</v>
+        <v>792</v>
       </c>
       <c r="H10" t="n">
         <v>0.75</v>
@@ -1346,7 +1346,7 @@
         <v>1.29</v>
       </c>
       <c r="O10" t="n">
-        <v>20230671625</v>
+        <v>20466552865</v>
       </c>
       <c r="P10" t="n">
         <v>21500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14350</v>
+        <v>14480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-1.97</v>
       </c>
       <c r="E11" t="n">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F11" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G11" t="n">
-        <v>592</v>
+        <v>636</v>
       </c>
       <c r="H11" t="n">
         <v>1.17</v>
@@ -1438,7 +1438,7 @@
         <v>3.14</v>
       </c>
       <c r="O11" t="n">
-        <v>97107241675</v>
+        <v>97850958580</v>
       </c>
       <c r="P11" t="n">
         <v>36200</v>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>이란-걸프국가 호르무즈 해협 회담 연기 및 국제 유가 폭등 관련주. 브렌트유 최고점, WTI 104달러 돌파 직전 상황. 외인, 기관, 프로그램 동반 매도 중.</t>
+          <t>이란-걸프국가 호르무즈 해협 회담 연기 및 국제 유가 급등에 따른 기대감. 외인, 기관 매도세 속 주가 하락.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1498,13 +1498,13 @@
         <v>-0.36</v>
       </c>
       <c r="E12" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F12" t="n">
         <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H12" t="n">
         <v>2.08</v>
@@ -1530,7 +1530,7 @@
         <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>14350975893</v>
+        <v>14507661917</v>
       </c>
       <c r="P12" t="n">
         <v>4795</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>88850</v>
+        <v>253500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-2.31%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>180</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>104</v>
+        <v>493</v>
       </c>
       <c r="G13" t="n">
-        <v>581</v>
+        <v>1705</v>
       </c>
       <c r="H13" t="n">
-        <v>23.56</v>
+        <v>46.64</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>90800</v>
+        <v>259500</v>
       </c>
       <c r="K13" t="n">
-        <v>89800</v>
+        <v>249500</v>
       </c>
       <c r="L13" t="n">
-        <v>90400</v>
+        <v>254500</v>
       </c>
       <c r="M13" t="n">
-        <v>87700</v>
+        <v>249000</v>
       </c>
       <c r="N13" t="n">
-        <v>23.59</v>
+        <v>46.71</v>
       </c>
       <c r="O13" t="n">
-        <v>136173954300</v>
+        <v>2068600490500</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>75900</v>
       </c>
       <c r="R13" t="n">
-        <v>-464000</v>
+        <v>-2179000</v>
       </c>
       <c r="S13" t="n">
-        <v>-70000</v>
+        <v>-1014000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국제 유가 상승 시 원전주 상승 가능성 언급, 9만원대 방어를 통한 기관 매수세 유입 기대감.</t>
+          <t>정치적 이슈에 따른 국장 전반에 대한 부정적 전망. HBM 개발 지연 및 주가 하락에 대한 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전주', '국제유가', '기관매수']</t>
+          <t>['국내주식', 'HBM', '주가하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253750</v>
+        <v>88600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>185</v>
       </c>
       <c r="F14" t="n">
-        <v>500</v>
+        <v>107</v>
       </c>
       <c r="G14" t="n">
-        <v>1733</v>
+        <v>593</v>
       </c>
       <c r="H14" t="n">
-        <v>46.64</v>
+        <v>23.56</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>259500</v>
+        <v>90800</v>
       </c>
       <c r="K14" t="n">
-        <v>249500</v>
+        <v>89800</v>
       </c>
       <c r="L14" t="n">
-        <v>254000</v>
+        <v>90400</v>
       </c>
       <c r="M14" t="n">
-        <v>249000</v>
+        <v>87700</v>
       </c>
       <c r="N14" t="n">
-        <v>46.71</v>
+        <v>23.59</v>
       </c>
       <c r="O14" t="n">
-        <v>1980152160250</v>
+        <v>138772096150</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>75900</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-2179000</v>
+        <v>-464000</v>
       </c>
       <c r="S14" t="n">
-        <v>-1014000</v>
+        <v>-70000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 부정적 전망 다수, HBM 개발 지연 가능성 및 전반적인 국내 증시 상황으로 인한 하락 위기 언급.</t>
+          <t>국제 유가 상승 시 원전주 상승 가능성 언급, 9만원대 방어를 통한 기관 매수세 유입 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치이슈', 'HBM', '하락']</t>
+          <t>['원전주', '국제유가', '기관매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11920</v>
+        <v>11930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.01%</t>
+          <t>-2.93%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.72</v>
       </c>
       <c r="E15" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H15" t="n">
         <v>0.22</v>
@@ -1806,7 +1806,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>52822907595</v>
+        <v>53107569845</v>
       </c>
       <c r="P15" t="n">
         <v>20850</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1736000</v>
+        <v>19070</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.19%</t>
+          <t>-4.12%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>57</v>
       </c>
       <c r="F16" t="n">
-        <v>524</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>1275</v>
+        <v>283</v>
       </c>
       <c r="H16" t="n">
-        <v>50.47</v>
+        <v>10.55</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1812000</v>
+        <v>19890</v>
       </c>
       <c r="K16" t="n">
-        <v>1707000</v>
+        <v>19480</v>
       </c>
       <c r="L16" t="n">
-        <v>1740000</v>
+        <v>19550</v>
       </c>
       <c r="M16" t="n">
-        <v>1695000</v>
+        <v>18780</v>
       </c>
       <c r="N16" t="n">
-        <v>50.55</v>
+        <v>10.65</v>
       </c>
       <c r="O16" t="n">
-        <v>3519549803500</v>
+        <v>49037197615</v>
       </c>
       <c r="P16" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>325000</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>-897000</v>
+        <v>-430000</v>
       </c>
       <c r="S16" t="n">
-        <v>-147000</v>
+        <v>-48000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>금리 인상 확정 시 불확실성 해소 기대. 외인 선물 매수 전환 및 175만원 회복 시 추세 회복 전망. 단기 하락 추세 및 150만원까지 하락 가능성 언급.</t>
+          <t>대차 해지 운동 및 공매도 세력과의 대립 구도 형성. 저점 매수 기회 및 주가 반등 기대감 언급, 투자자 참여 독려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['금리인상', '외인매수', '추세회복']</t>
+          <t>['대차 해지', '공매도', '반등 기대']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19040</v>
+        <v>1727000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.27%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>54</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>33</v>
+        <v>525</v>
       </c>
       <c r="G17" t="n">
-        <v>268</v>
+        <v>1269</v>
       </c>
       <c r="H17" t="n">
-        <v>10.55</v>
+        <v>50.47</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,91 +1975,91 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>19890</v>
+        <v>1812000</v>
       </c>
       <c r="K17" t="n">
-        <v>19480</v>
+        <v>1707000</v>
       </c>
       <c r="L17" t="n">
-        <v>19550</v>
+        <v>1740000</v>
       </c>
       <c r="M17" t="n">
-        <v>18780</v>
+        <v>1695000</v>
       </c>
       <c r="N17" t="n">
-        <v>10.65</v>
+        <v>50.55</v>
       </c>
       <c r="O17" t="n">
-        <v>48061633310</v>
+        <v>3591642071500</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>325000</v>
       </c>
       <c r="R17" t="n">
-        <v>-430000</v>
+        <v>-897000</v>
       </c>
       <c r="S17" t="n">
-        <v>-48000</v>
+        <v>-147000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대차 해지 운동 및 공매도 세력과의 대립 구도 형성. 저점 매수 기회 및 주가 반등 기대감 언급, 투자자 참여 독려.</t>
+          <t>금리 인상 불확실성 해소 기대감 속 개인 투자자의 불안감. 향후 주가 추가 하락 가능성에 대한 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '반등 기대']</t>
+          <t>['금리인상', '개미', '주가전망']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13980</v>
+        <v>11820</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.96%</t>
+          <t>-5.06%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>17.58</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14710</v>
+        <v>12450</v>
       </c>
       <c r="K18" t="n">
-        <v>14710</v>
+        <v>11960</v>
       </c>
       <c r="L18" t="n">
-        <v>15420</v>
+        <v>13900</v>
       </c>
       <c r="M18" t="n">
-        <v>13700</v>
+        <v>11800</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>17.07</v>
       </c>
       <c r="O18" t="n">
-        <v>24573659895</v>
+        <v>54956368010</v>
       </c>
       <c r="P18" t="n">
-        <v>19380</v>
+        <v>14350</v>
       </c>
       <c r="Q18" t="n">
-        <v>3200</v>
+        <v>465</v>
       </c>
       <c r="R18" t="n">
-        <v>-67000</v>
+        <v>-51000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>수원 파장1구역 재건축 시공사 선정 소식에도 불구하고, 부동산 시장 침체 및 외인 매도세로 주가 하락. 1만원대 지지선 약화 우려.</t>
+          <t>외국인 대량 매수세 유입되며 급등 기대감 형성. 단기 급등 후 주가 조정 및 변동성 확대, 수급 변화 주목.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['재건축', '부동산 침체', '외인 매도']</t>
+          <t>['외국인 매수', '급등 기대', '주가 변동성']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11830</v>
+        <v>13910</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.98%</t>
+          <t>-5.44%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F19" t="n">
         <v>44</v>
       </c>
       <c r="G19" t="n">
-        <v>134</v>
+        <v>201</v>
       </c>
       <c r="H19" t="n">
-        <v>17.58</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>12450</v>
+        <v>14710</v>
       </c>
       <c r="K19" t="n">
-        <v>11960</v>
+        <v>14710</v>
       </c>
       <c r="L19" t="n">
-        <v>13900</v>
+        <v>15420</v>
       </c>
       <c r="M19" t="n">
-        <v>11800</v>
+        <v>13700</v>
       </c>
       <c r="N19" t="n">
-        <v>17.07</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>54437744560</v>
+        <v>24740800445</v>
       </c>
       <c r="P19" t="n">
-        <v>14350</v>
+        <v>19380</v>
       </c>
       <c r="Q19" t="n">
-        <v>465</v>
+        <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>-51000</v>
+        <v>-67000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>외국인 대량 매수세 유입되며 급등 기대감 형성. 단기 급등 후 주가 조정 및 변동성 확대, 수급 변화 주목.</t>
+          <t>수원 파장1구역 재건축 시공사 선정 소식에도 불구하고, 부동산 시장 침체 및 외인 매도세로 주가 하락. 1만원대 지지선 약화 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['외국인 매수', '급등 기대', '주가 변동성']</t>
+          <t>['재건축', '부동산 침체', '외인 매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>002990</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260914_11.xlsx
+++ b/data/trending_integrated_20260914_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9920</v>
+        <v>9800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+25.57%</t>
+          <t>+24.05%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F2" t="n">
         <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>220750858680</v>
+        <v>228604542390</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 테마 상승 기대감. SK하이닉스 CPO 광원 관련 이슈 부각.</t>
+          <t>차세대 광반도체 관련주로서 프로그램 매수세 유입에 따른 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', 'CPO']</t>
+          <t>['광전자', '광반도체', '프로그램']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6510</v>
+        <v>6620</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+18.15%</t>
+          <t>+20.15%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
         <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>47837793575</v>
+        <v>48390941230</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9140</v>
+        <v>8920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.25%</t>
+          <t>+12.77%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01</v>
+        <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="H4" t="n">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8290</v>
+        <v>7910</v>
       </c>
       <c r="K4" t="n">
-        <v>8300</v>
+        <v>7800</v>
       </c>
       <c r="L4" t="n">
-        <v>9425</v>
+        <v>9840</v>
       </c>
       <c r="M4" t="n">
-        <v>8300</v>
+        <v>7540</v>
       </c>
       <c r="N4" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>30631662910</v>
+        <v>63134846585</v>
       </c>
       <c r="P4" t="n">
-        <v>12800</v>
+        <v>25050</v>
       </c>
       <c r="Q4" t="n">
-        <v>5340</v>
+        <v>3705</v>
       </c>
       <c r="R4" t="n">
-        <v>447000</v>
+        <v>-24000</v>
       </c>
       <c r="S4" t="n">
-        <v>127000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>폴더블폰 시장 확대에 따른 수혜 기대감, 그러나 단기 차익 실현 및 전환사채 관련 이슈로 인한 변동성.</t>
+          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['폴더블', '매출 증', '전환사채']</t>
+          <t>['펩타이드', '특허 등록', '면역 조절']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8670</v>
+        <v>9110</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+9.61%</t>
+          <t>+9.89%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.55</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>66</v>
+        <v>178</v>
       </c>
       <c r="H5" t="n">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7910</v>
+        <v>8290</v>
       </c>
       <c r="K5" t="n">
-        <v>7800</v>
+        <v>8300</v>
       </c>
       <c r="L5" t="n">
-        <v>9840</v>
+        <v>9425</v>
       </c>
       <c r="M5" t="n">
-        <v>7540</v>
+        <v>8300</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="O5" t="n">
-        <v>59298170690</v>
+        <v>31116167935</v>
       </c>
       <c r="P5" t="n">
-        <v>25050</v>
+        <v>12800</v>
       </c>
       <c r="Q5" t="n">
-        <v>3705</v>
+        <v>5340</v>
       </c>
       <c r="R5" t="n">
-        <v>-24000</v>
+        <v>447000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
+          <t>폴더블폰 시장 확대에 따른 수혜 기대감, 그러나 단기 차익 실현 및 전환사채 관련 이슈로 인한 변동성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['펩타이드', '특허 등록', '면역 조절']</t>
+          <t>['폴더블', '매출 증', '전환사채']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>441270</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4210</v>
+        <v>4140</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+8.79%</t>
+          <t>+6.98%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="H6" t="n">
         <v>0.59</v>
@@ -978,7 +978,7 @@
         <v>1.04</v>
       </c>
       <c r="O6" t="n">
-        <v>108400494335</v>
+        <v>118734768095</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2775</v>
+        <v>2790</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+5.92%</t>
+          <t>+6.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-2.39</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="H7" t="n">
         <v>1.44</v>
@@ -1070,7 +1070,7 @@
         <v>3.83</v>
       </c>
       <c r="O7" t="n">
-        <v>89828146664</v>
+        <v>90468456434</v>
       </c>
       <c r="P7" t="n">
         <v>4810</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16760</v>
+        <v>17020</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+4.36%</t>
+          <t>+5.98%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H8" t="n">
         <v>2.7</v>
@@ -1162,7 +1162,7 @@
         <v>2.39</v>
       </c>
       <c r="O8" t="n">
-        <v>243632765620</v>
+        <v>245656566910</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론 관련 논쟁 속 양자 보안 테마 기대감. 주가 변동성 속 매물대 정리.</t>
+          <t>AI 개발 속도 조절론으로 인한 등락 속에 지지선 이탈 및 반등 시도 관측.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '양자보안', '매물대']</t>
+          <t>['엑스게이트', 'AI', '속도 조절론']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14650</v>
+        <v>14490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>+2.40%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="H9" t="n">
         <v>1.88</v>
@@ -1239,28 +1239,28 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14740</v>
+        <v>14150</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>13850</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>14730</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>13800</v>
       </c>
       <c r="N9" t="n">
         <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>90132000000</v>
+        <v>94711374240</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R9" t="n">
         <v>-430000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AIDC 및 광통신 기술 성장 전망. GPU 확보에 이은 연결성 강화 관련 긍정적 뉴스.</t>
+          <t>AIDC 광통신 기술 발전과 GPU 확보 소식을 바탕으로 한 대장주 광전자와의 동반 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', 'GPU']</t>
+          <t>['대한광통신', '광통신', 'AIDC']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8230</v>
+        <v>14550</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.54</v>
+        <v>-1.97</v>
       </c>
       <c r="E10" t="n">
-        <v>129</v>
+        <v>238</v>
       </c>
       <c r="F10" t="n">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="G10" t="n">
-        <v>792</v>
+        <v>624</v>
       </c>
       <c r="H10" t="n">
-        <v>0.75</v>
+        <v>1.17</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>8290</v>
+        <v>14610</v>
       </c>
       <c r="K10" t="n">
-        <v>8100</v>
+        <v>15420</v>
       </c>
       <c r="L10" t="n">
-        <v>9050</v>
+        <v>16510</v>
       </c>
       <c r="M10" t="n">
-        <v>8060</v>
+        <v>14320</v>
       </c>
       <c r="N10" t="n">
-        <v>1.29</v>
+        <v>3.14</v>
       </c>
       <c r="O10" t="n">
-        <v>20466552865</v>
+        <v>98580442970</v>
       </c>
       <c r="P10" t="n">
-        <v>21500</v>
+        <v>36200</v>
       </c>
       <c r="Q10" t="n">
-        <v>2300</v>
+        <v>8920</v>
       </c>
       <c r="R10" t="n">
-        <v>64000</v>
+        <v>-128000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>암 치료 바이오 신약 관련주로, '가짜내성' 타깃 항암 전략 제시. 글로벌 심포지엄 개최 및 탑급 교수 발표. 재료 핵폭탄급, 낮은 시총 기반 급등 기대.</t>
+          <t>이란-걸프국가 호르무즈 해협 회담 연기 및 국제 유가 급등을 근거로 한 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['항암', '바이오신약', '심포지엄']</t>
+          <t>['흥구석유', '국제 유가', '호르무즈']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14480</v>
+        <v>8190</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.97</v>
+        <v>-0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>242</v>
+        <v>132</v>
       </c>
       <c r="F11" t="n">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="G11" t="n">
-        <v>636</v>
+        <v>810</v>
       </c>
       <c r="H11" t="n">
-        <v>1.17</v>
+        <v>0.75</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14610</v>
+        <v>8290</v>
       </c>
       <c r="K11" t="n">
-        <v>15420</v>
+        <v>8100</v>
       </c>
       <c r="L11" t="n">
-        <v>16510</v>
+        <v>9050</v>
       </c>
       <c r="M11" t="n">
-        <v>14320</v>
+        <v>8060</v>
       </c>
       <c r="N11" t="n">
-        <v>3.14</v>
+        <v>1.29</v>
       </c>
       <c r="O11" t="n">
-        <v>97850958580</v>
+        <v>20692507995</v>
       </c>
       <c r="P11" t="n">
-        <v>36200</v>
+        <v>21500</v>
       </c>
       <c r="Q11" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R11" t="n">
-        <v>-128000</v>
+        <v>64000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>이란-걸프국가 호르무즈 해협 회담 연기 및 국제 유가 급등에 따른 기대감. 외인, 기관 매도세 속 주가 하락.</t>
+          <t>항암 신약 관련 글로벌 심포지엄 개최 및 임상 결과에 대한 기대감으로 인한 목표가 상향 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '회담연기']</t>
+          <t>['페니트리움바이오', '항암 신약', '임상']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1843</v>
+        <v>1851</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.36</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H12" t="n">
         <v>2.08</v>
@@ -1530,7 +1530,7 @@
         <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>14507661917</v>
+        <v>14556961798</v>
       </c>
       <c r="P12" t="n">
         <v>4795</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253500</v>
+        <v>253750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G13" t="n">
-        <v>1705</v>
+        <v>1722</v>
       </c>
       <c r="H13" t="n">
         <v>46.64</v>
@@ -1622,7 +1622,7 @@
         <v>46.71</v>
       </c>
       <c r="O13" t="n">
-        <v>2068600490500</v>
+        <v>2122074113000</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈에 따른 국장 전반에 대한 부정적 전망. HBM 개발 지연 및 주가 하락에 대한 우려.</t>
+          <t>정치적 이슈와 연계된 부정적 전망과 함께 주가 하락 우려 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['국내주식', 'HBM', '주가하락']</t>
+          <t>['삼성전자', '정치', '주가 하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,13 +1682,13 @@
         <v>-0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G14" t="n">
-        <v>593</v>
+        <v>615</v>
       </c>
       <c r="H14" t="n">
         <v>23.56</v>
@@ -1714,7 +1714,7 @@
         <v>23.59</v>
       </c>
       <c r="O14" t="n">
-        <v>138772096150</v>
+        <v>140210842950</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>국제 유가 상승 시 원전주 상승 가능성 언급, 9만원대 방어를 통한 기관 매수세 유입 기대감.</t>
+          <t>국제 유가 상승과 정부 정책 지원을 근거로 한 단기 반등 및 급등 구간 진입 가능성 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전주', '국제유가', '기관매수']</t>
+          <t>['두산에너빌리티', '국제 유가', '원전']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11930</v>
+        <v>11940</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.72</v>
       </c>
       <c r="E15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H15" t="n">
         <v>0.22</v>
@@ -1806,7 +1806,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>53107569845</v>
+        <v>53358963895</v>
       </c>
       <c r="P15" t="n">
         <v>20850</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19070</v>
+        <v>1736000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.12%</t>
+          <t>-4.19%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>57</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>35</v>
+        <v>521</v>
       </c>
       <c r="G16" t="n">
-        <v>283</v>
+        <v>1241</v>
       </c>
       <c r="H16" t="n">
-        <v>10.55</v>
+        <v>50.47</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>19890</v>
+        <v>1812000</v>
       </c>
       <c r="K16" t="n">
-        <v>19480</v>
+        <v>1707000</v>
       </c>
       <c r="L16" t="n">
-        <v>19550</v>
+        <v>1740000</v>
       </c>
       <c r="M16" t="n">
-        <v>18780</v>
+        <v>1695000</v>
       </c>
       <c r="N16" t="n">
-        <v>10.65</v>
+        <v>50.55</v>
       </c>
       <c r="O16" t="n">
-        <v>49037197615</v>
+        <v>3665724575500</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>325000</v>
       </c>
       <c r="R16" t="n">
-        <v>-430000</v>
+        <v>-897000</v>
       </c>
       <c r="S16" t="n">
-        <v>-48000</v>
+        <v>-147000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대차 해지 운동 및 공매도 세력과의 대립 구도 형성. 저점 매수 기회 및 주가 반등 기대감 언급, 투자자 참여 독려.</t>
+          <t>금리 인상 관련 불확실성 해소 기대감과 함께 주가 추가 하락 가능성 언급. 일부 매수세 유입.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '반등 기대']</t>
+          <t>['SK하이닉스', '금리 인상', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1727000</v>
+        <v>19000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.69%</t>
+          <t>-4.47%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>59</v>
       </c>
       <c r="F17" t="n">
-        <v>525</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>1269</v>
+        <v>294</v>
       </c>
       <c r="H17" t="n">
-        <v>50.47</v>
+        <v>10.55</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,60 +1975,60 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1812000</v>
+        <v>19890</v>
       </c>
       <c r="K17" t="n">
-        <v>1707000</v>
+        <v>19480</v>
       </c>
       <c r="L17" t="n">
-        <v>1740000</v>
+        <v>19550</v>
       </c>
       <c r="M17" t="n">
-        <v>1695000</v>
+        <v>18780</v>
       </c>
       <c r="N17" t="n">
-        <v>50.55</v>
+        <v>10.65</v>
       </c>
       <c r="O17" t="n">
-        <v>3591642071500</v>
+        <v>49813853225</v>
       </c>
       <c r="P17" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q17" t="n">
-        <v>325000</v>
+        <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>-897000</v>
+        <v>-430000</v>
       </c>
       <c r="S17" t="n">
-        <v>-147000</v>
+        <v>-48000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>금리 인상 불확실성 해소 기대감 속 개인 투자자의 불안감. 향후 주가 추가 하락 가능성에 대한 언급.</t>
+          <t>대차 해지 운동 및 공매도 세력과의 대립 구도 형성. 저점 매수 기회 및 주가 반등 기대감 언급, 투자자 참여 독려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['금리인상', '개미', '주가전망']</t>
+          <t>['대차 해지', '공매도', '반등 기대']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11820</v>
+        <v>11870</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.06%</t>
+          <t>-4.66%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H18" t="n">
         <v>17.58</v>
@@ -2082,7 +2082,7 @@
         <v>17.07</v>
       </c>
       <c r="O18" t="n">
-        <v>54956368010</v>
+        <v>55201090400</v>
       </c>
       <c r="P18" t="n">
         <v>14350</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13910</v>
+        <v>13940</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.44%</t>
+          <t>-5.23%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>24740800445</v>
+        <v>24999113710</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
